--- a/test_transactions.xlsx
+++ b/test_transactions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F135"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>platformProductID</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>platformPrice</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>purchase_bid_value</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>timestamp</t>
         </is>
@@ -470,18 +475,23 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0.01621801890483265</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:02</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -494,18 +504,23 @@
       <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D3" t="n">
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0.02388750612100754</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:02</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -518,18 +533,23 @@
       <c r="C4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D4" t="n">
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0.07135750337504831</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:03</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -542,18 +562,23 @@
       <c r="C5" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D5" t="n">
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0.1083604156050173</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:03</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -566,18 +591,23 @@
       <c r="C6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D6" t="n">
+        <v>1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1281271865968059</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:03</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -590,18 +620,23 @@
       <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D7" t="n">
+        <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0.1447772750762504</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:04</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -614,18 +649,23 @@
       <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D8" t="n">
+        <v>1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0.147375007939568</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:04</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -638,18 +678,23 @@
       <c r="C9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D9" t="n">
+        <v>1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1816841225889396</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:04</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -662,18 +707,23 @@
       <c r="C10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D10" t="n">
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>0.1902450527344349</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:05</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -686,18 +736,23 @@
       <c r="C11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D11" t="n">
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>0.1941621819777214</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:05</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -710,18 +765,23 @@
       <c r="C12" t="n">
         <v>1</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D12" t="n">
+        <v>1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>0.1975612330774323</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:05</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -734,18 +794,23 @@
       <c r="C13" t="n">
         <v>1</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D13" t="n">
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0.2304162030427914</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:06</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -758,18 +823,23 @@
       <c r="C14" t="n">
         <v>1</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D14" t="n">
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.2478704783730667</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:07</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -782,18 +852,23 @@
       <c r="C15" t="n">
         <v>1</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D15" t="n">
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0.2853630710388065</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:08</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -806,18 +881,23 @@
       <c r="C16" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D16" t="n">
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.3693513539224142</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:13</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -830,18 +910,23 @@
       <c r="C17" t="n">
         <v>1</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D17" t="n">
+        <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0.4019703003803058</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:14</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -854,18 +939,23 @@
       <c r="C18" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D18" t="n">
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0.4088319664571577</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:15</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -878,18 +968,23 @@
       <c r="C19" t="n">
         <v>1</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D19" t="n">
+        <v>1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0.4547990804244468</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:17</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -902,18 +997,23 @@
       <c r="C20" t="n">
         <v>1</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D20" t="n">
+        <v>1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>0.4585744908683151</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:18</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -926,18 +1026,23 @@
       <c r="C21" t="n">
         <v>1</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D21" t="n">
+        <v>1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0.4711672816633374</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:18</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -950,18 +1055,23 @@
       <c r="C22" t="n">
         <v>1</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D22" t="n">
+        <v>1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0.508576673300835</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:19</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -974,18 +1084,23 @@
       <c r="C23" t="n">
         <v>1</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D23" t="n">
+        <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0.5329613374366037</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:20</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -998,18 +1113,23 @@
       <c r="C24" t="n">
         <v>1</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D24" t="n">
+        <v>1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0.5458136774543901</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:29</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1022,18 +1142,23 @@
       <c r="C25" t="n">
         <v>1</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D25" t="n">
+        <v>1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0.5538748539233053</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:34</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1046,18 +1171,23 @@
       <c r="C26" t="n">
         <v>1</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D26" t="n">
+        <v>1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>0.5839968608211856</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:35</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1070,18 +1200,23 @@
       <c r="C27" t="n">
         <v>1</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D27" t="n">
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0.5930123062829421</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:36</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1094,18 +1229,23 @@
       <c r="C28" t="n">
         <v>1</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D28" t="n">
+        <v>1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0.6146913327140828</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:36</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1118,18 +1258,23 @@
       <c r="C29" t="n">
         <v>1</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D29" t="n">
+        <v>1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0.6210330280274692</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:36</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1142,18 +1287,23 @@
       <c r="C30" t="n">
         <v>1</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D30" t="n">
+        <v>1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>0.6223752195256791</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:37</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1166,18 +1316,23 @@
       <c r="C31" t="n">
         <v>1</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D31" t="n">
+        <v>1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>0.6245510621458654</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:37</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1190,18 +1345,23 @@
       <c r="C32" t="n">
         <v>1</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D32" t="n">
+        <v>1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0.6418554281780483</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:37</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1214,18 +1374,23 @@
       <c r="C33" t="n">
         <v>1</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D33" t="n">
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>0.6543831154045805</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:38</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -1238,18 +1403,23 @@
       <c r="C34" t="n">
         <v>1</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D34" t="n">
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0.6857226635098115</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:38</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1262,18 +1432,23 @@
       <c r="C35" t="n">
         <v>1</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D35" t="n">
+        <v>1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>0.7436748764411355</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:39</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -1286,18 +1461,23 @@
       <c r="C36" t="n">
         <v>1</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D36" t="n">
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>0.7444883646671228</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:40</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1310,18 +1490,23 @@
       <c r="C37" t="n">
         <v>1</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D37" t="n">
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>0.7528633396504397</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:42</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1334,18 +1519,23 @@
       <c r="C38" t="n">
         <v>1</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D38" t="n">
+        <v>1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>0.7546463927217041</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:42</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1358,18 +1548,23 @@
       <c r="C39" t="n">
         <v>1</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D39" t="n">
+        <v>1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>0.7782752817790498</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:45</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -1382,18 +1577,23 @@
       <c r="C40" t="n">
         <v>1</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D40" t="n">
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>0.8095139766752179</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:45</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1406,18 +1606,23 @@
       <c r="C41" t="n">
         <v>1</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D41" t="n">
+        <v>1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>0.8125159364381074</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:47</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -1430,18 +1635,23 @@
       <c r="C42" t="n">
         <v>1</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D42" t="n">
+        <v>1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0.9303249018864177</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:50</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1454,18 +1664,23 @@
       <c r="C43" t="n">
         <v>1</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D43" t="n">
+        <v>1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>0.9817390892302099</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:50</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -1478,18 +1693,23 @@
       <c r="C44" t="n">
         <v>1</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D44" t="n">
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>0.9860863707653654</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:51</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1502,16 +1722,23 @@
       <c r="C45" t="n">
         <v>1</v>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>131.52</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.05610204378124128</v>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:52</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1524,18 +1751,23 @@
       <c r="C46" t="n">
         <v>1</v>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D46" t="n">
+        <v>1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>0.1265473438079386</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:54</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1548,16 +1780,23 @@
       <c r="C47" t="n">
         <v>1</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>110.86</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.13002918797295</v>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:57</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1570,16 +1809,23 @@
       <c r="C48" t="n">
         <v>1</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>123.21</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.187454629811622</v>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:58</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1592,18 +1838,23 @@
       <c r="C49" t="n">
         <v>1</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D49" t="n">
+        <v>1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>0.1921474992245124</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:58</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -1616,16 +1867,23 @@
       <c r="C50" t="n">
         <v>1</v>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>106.96</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.2044222919745743</v>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:58</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1638,16 +1896,23 @@
       <c r="C51" t="n">
         <v>1</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>116.73</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.2647250395997391</v>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:59</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1655,21 +1920,28 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>117.71</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0.2964023478317959</v>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:03</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -1677,23 +1949,28 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D53" t="n">
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>0.3805659452362748</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:04</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1701,21 +1978,28 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>134.59</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0.3808921906839496</v>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:05</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1723,23 +2007,28 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D55" t="n">
+        <v>1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>0.4643391440485948</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:06</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1747,21 +2036,28 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>118.44</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.4963322480485769</v>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:08</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1769,23 +2065,28 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D57" t="n">
+        <v>1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>0.5972476008943898</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:08</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -1793,23 +2094,28 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D58" t="n">
+        <v>1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>0.6732222683853338</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:08</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1817,23 +2123,28 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D59" t="n">
+        <v>1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>0.7371375963130586</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:08</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -1841,21 +2152,28 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>125.68</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.7590744429984232</v>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:13</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -1863,21 +2181,28 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>127.97</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.8188839349647687</v>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:14</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -1885,21 +2210,28 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>127.17</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.8402014590051923</v>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:17</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -1907,21 +2239,28 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>134.78</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.8791190388529467</v>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:18</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1929,23 +2268,28 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D64" t="n">
+        <v>1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>0.898997724970381</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:18</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -1953,23 +2297,28 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D65" t="n">
+        <v>1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>0.8996331851234589</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:19</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -1977,23 +2326,28 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D66" t="n">
+        <v>1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>0.9320593246803855</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:19</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -2001,21 +2355,28 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>124.16</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.9524139469484307</v>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:20</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -2023,23 +2384,28 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D68" t="n">
+        <v>1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>0.9618049919677664</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:23</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -2047,23 +2413,28 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D69" t="n">
+        <v>1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>0.2085662129174564</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:24</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -2071,23 +2442,28 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D70" t="n">
+        <v>1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>0.460262509050735</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:28</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -2095,23 +2471,28 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D71" t="n">
+        <v>1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>0.6672108541756523</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:29</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -2119,23 +2500,28 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D72" t="n">
+        <v>1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>0.6751668078352364</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:30</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -2143,23 +2529,28 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D73" t="n">
+        <v>1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>0.7256690588352414</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:31</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -2167,23 +2558,28 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D74" t="n">
+        <v>1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>0.7556186655340433</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:31</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -2191,23 +2587,28 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D75" t="n">
+        <v>1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>0.8686886550304241</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:31</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -2215,23 +2616,28 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D76" t="n">
+        <v>1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>0.8960173190567295</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:33</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -2239,23 +2645,28 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
+      <c r="D77" t="n">
+        <v>1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>0.9972253088986182</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:34</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -2263,23 +2674,28 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D78" t="n">
+        <v>1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>0.07032333319278061</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:34</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -2287,23 +2703,28 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D79" t="n">
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>0.09133907670467545</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:39</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -2311,21 +2732,28 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.1104865315189072</v>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:39</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -2333,23 +2761,28 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D81" t="n">
+        <v>1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>0.1231460131257408</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:42</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -2357,23 +2790,28 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D82" t="n">
+        <v>1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>0.1482656560371628</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:42</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -2381,23 +2819,28 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D83" t="n">
+        <v>1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>0.1665381787906349</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:44</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -2405,21 +2848,28 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>119.83</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0.1802223758313949</v>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:46</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -2427,21 +2877,28 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>130.49</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0.2069728831103498</v>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:46</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -2449,21 +2906,28 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>86.26000000000001</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0.2075962626329091</v>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:46</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -2471,23 +2935,28 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D87" t="n">
+        <v>1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>0.2155617073431958</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:47</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -2495,21 +2964,28 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>112.65</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0.2308169041431007</v>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:49</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -2517,21 +2993,28 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>91.26000000000001</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0.2344989562106252</v>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:52</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -2539,23 +3022,28 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D90" t="n">
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>0.3090345833714554</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:52</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -2563,21 +3051,28 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>103.87</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0.3246401972921068</v>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:53</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -2585,21 +3080,28 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
-        <v>82.56999999999999</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0.3641220007301822</v>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:54</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -2607,21 +3109,28 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E93" t="n">
-        <v>117.53</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0.3672470215122954</v>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:57</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -2629,21 +3138,28 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>127.37</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0.3769937372691932</v>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:58</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -2651,21 +3167,28 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>96.79000000000001</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0.3975315826778815</v>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:59</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -2673,21 +3196,28 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>118.43</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0.4024886040820366</v>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:01</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -2695,23 +3225,28 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D97" t="n">
+        <v>1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>0.4588699052172552</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:03</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -2719,21 +3254,28 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>114.59</v>
-      </c>
-      <c r="F98" t="n">
-        <v>0.4825463759432371</v>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:04</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -2741,23 +3283,28 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D99" t="n">
+        <v>1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>0.4908562637403427</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:05</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -2765,21 +3312,28 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>85.95</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0.5038208086358112</v>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:11</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -2787,21 +3341,28 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>96.73999999999999</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0.5317382086049129</v>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:13</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -2809,21 +3370,28 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>109.35</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0.5324063925295354</v>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:19</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -2831,21 +3399,28 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>96.04000000000001</v>
-      </c>
-      <c r="F103" t="n">
-        <v>0.5416392221547873</v>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:19</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -2853,23 +3428,28 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D104" t="n">
+        <v>1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>0.6241917328679618</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:24</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -2877,21 +3457,28 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
-        <v>88.70999999999999</v>
-      </c>
-      <c r="F105" t="n">
-        <v>0.6258300404638315</v>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:25</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -2899,21 +3486,28 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
-        <v>89.12</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0.7201121880839255</v>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:26</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -2921,23 +3515,28 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D107" t="n">
+        <v>1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>0.7265897949263399</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:28</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -2945,21 +3544,28 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>113.49</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0.7609517321209563</v>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:29</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -2967,23 +3573,28 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D109" t="n">
+        <v>1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>0.7713549397463741</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:30</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -2991,23 +3602,28 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C110" t="n">
         <v>1</v>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D110" t="n">
+        <v>1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>0.7752535244006271</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:31</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -3015,21 +3631,28 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C111" t="n">
         <v>1</v>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>103.67</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0.7819186226562179</v>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:32</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -3037,23 +3660,28 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C112" t="n">
         <v>1</v>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D112" t="n">
+        <v>1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
-        <v>0.81341485446694</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:32</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -3061,21 +3689,28 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>99.33</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0.8340500881225812</v>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:34</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -3083,23 +3718,28 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D114" t="n">
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>0.8415386072459383</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:34</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -3107,23 +3747,28 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D115" t="n">
+        <v>1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>0.8779064647152706</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:34</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -3131,23 +3776,28 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D116" t="n">
+        <v>1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>0.8913761347214296</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:41</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -3155,23 +3805,28 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D117" t="n">
+        <v>1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>0.9405320208199482</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:41</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -3179,21 +3834,28 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
-        <v>113.3</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0.9406930218487978</v>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:43</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -3201,23 +3863,28 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D119" t="n">
+        <v>1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>0.969392017769046</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:47</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -3225,23 +3892,28 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D120" t="n">
+        <v>1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>0.03867476410471293</v>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:55</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -3249,23 +3921,28 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="inlineStr">
         <is>
           <t>PN</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>0.08341658843237909</v>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:00</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -3273,21 +3950,28 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E122" t="n">
-        <v>131.32</v>
-      </c>
-      <c r="F122" t="n">
-        <v>0.08873774933029133</v>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:04</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -3295,23 +3979,26 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D123" t="n">
+        <v>1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0.1784642244195833</v>
+        <v>162.16</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:04</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -3319,21 +4006,28 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
-        <v>106.19</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0.1915586621580841</v>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:05</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -3341,23 +4035,28 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr">
         <is>
           <t>PN</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>0.2262488307625372</v>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:05</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -3365,21 +4064,26 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="inlineStr">
         <is>
           <t>BID</t>
         </is>
       </c>
-      <c r="E126" t="n">
-        <v>90.26000000000001</v>
-      </c>
       <c r="F126" t="n">
-        <v>0.235578664764719</v>
+        <v>136.68</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:06</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -3387,23 +4091,28 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
         <is>
           <t>PN</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>0.4010456165497788</v>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:06</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -3411,21 +4120,26 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="inlineStr">
         <is>
           <t>BID</t>
         </is>
       </c>
-      <c r="E128" t="n">
-        <v>109.9</v>
-      </c>
       <c r="F128" t="n">
-        <v>0.4149389929988377</v>
+        <v>122.98</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:06</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -3433,23 +4147,28 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>PN</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>0.4345027370758671</v>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:07</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -3457,23 +4176,26 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D130" t="n">
+        <v>1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="F130" t="n">
-        <v>0.4857124030671724</v>
+        <v>136.57</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:07</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -3481,23 +4203,26 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>PN</t>
-        </is>
+      <c r="D131" t="n">
+        <v>1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>0.4888642933893973</v>
+        <v>173.32</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:07</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -3505,21 +4230,28 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0.5295366877774511</v>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:11</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -3527,21 +4259,26 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
         <is>
           <t>BID</t>
         </is>
       </c>
-      <c r="E133" t="n">
-        <v>124.57</v>
-      </c>
       <c r="F133" t="n">
-        <v>0.6702704119606171</v>
+        <v>166.33</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:11</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -3549,23 +4286,28 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
         <is>
           <t>PN</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F134" t="n">
-        <v>0.888011002964412</v>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:12</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -3573,21 +4315,1158 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="inlineStr">
         <is>
           <t>BID</t>
         </is>
       </c>
-      <c r="E135" t="n">
-        <v>115.28</v>
-      </c>
       <c r="F135" t="n">
-        <v>0.8943215779469837</v>
+        <v>153.47</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>4</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>4</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>142.49</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>4</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>166.45</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>4</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>164.57</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>4</v>
+      </c>
+      <c r="C140" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>163.4</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>4</v>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>4</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>4</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>4</v>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>4</v>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>135.16</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>4</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>166.27</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>4</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>4</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>169.36</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>4</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>4</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>111.56</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>4</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>108.32</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>4</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>4</v>
+      </c>
+      <c r="C153" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>126.27</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>4</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>4</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>4</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>129.19</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>4</v>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>4</v>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>4</v>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>4</v>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>153.85</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>4</v>
+      </c>
+      <c r="C161" t="n">
+        <v>1</v>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>4</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>4</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>4</v>
+      </c>
+      <c r="C164" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>PN</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>4</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>153.77</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>4</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>135.21</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>5</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>5</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>5</v>
+      </c>
+      <c r="C169" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>5</v>
+      </c>
+      <c r="C170" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>5</v>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>5</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>5</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>5</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>5</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>15/01/2025 00:54</t>
+        </is>
       </c>
     </row>
   </sheetData>
